--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI31"/>
+  <dimension ref="A1:BI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,27 +945,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46161.35763888889</v>
+        <v>46161.35416666666</v>
       </c>
     </row>
     <row r="4">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46161.375</v>
+        <v>46161.35763888889</v>
       </c>
     </row>
     <row r="6">
@@ -1733,27 +1733,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46161.41666666666</v>
+        <v>46161.375</v>
       </c>
     </row>
     <row r="8">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46161.5</v>
+        <v>46161.41666666666</v>
       </c>
     </row>
     <row r="10">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2521,27 +2521,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46161.54166666666</v>
+        <v>46161.5</v>
       </c>
     </row>
     <row r="12">
@@ -2718,27 +2718,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46161.57291666666</v>
+        <v>46161.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2915,27 +2915,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46161.58333333334</v>
+        <v>46161.57291666666</v>
       </c>
     </row>
     <row r="14">
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46161.60416666666</v>
+        <v>46161.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46161.64583333334</v>
+        <v>46161.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46161.66666666666</v>
+        <v>46161.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46161.67708333334</v>
+        <v>46161.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46161.875</v>
+        <v>46161.67708333334</v>
       </c>
     </row>
     <row r="24">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,6 +6649,203 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
+        <v>46161.875</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="3" t="n">
         <v>46161.875</v>
       </c>
     </row>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI32"/>
+  <dimension ref="A1:BI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46161.64583333334</v>
+        <v>46161.625</v>
       </c>
     </row>
     <row r="19">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46161.66666666666</v>
+        <v>46161.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46161.67708333334</v>
+        <v>46161.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46161.875</v>
+        <v>46161.67708333334</v>
       </c>
     </row>
     <row r="25">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,6 +6846,203 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
+        <v>46161.875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" s="3" t="n">
         <v>46161.875</v>
       </c>
     </row>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>4.02</v>
       </c>
       <c r="R22" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="R20" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="R21" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.02</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.77</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="R20" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI33"/>
+  <dimension ref="A1:BI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.02</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>4.02</v>
       </c>
       <c r="R22" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5271,1779 +5271,6 @@
       </c>
       <c r="BI24" s="3" t="n">
         <v>46161.67708333334</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Al Khaleej</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Al Ahli</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI25" s="3" t="n">
-        <v>46161.875</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Al Najma</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Al Shabab</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI26" s="3" t="n">
-        <v>46161.875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Al Hazm</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Al Taawon</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI27" s="3" t="n">
-        <v>46161.875</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Neom SC</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Al Ittifaq</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI28" s="3" t="n">
-        <v>46161.875</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Al Ittihad</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Al Quadisiya</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="3" t="n">
-        <v>46161.875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Al Kholood</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Al Fateh</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="3" t="n">
-        <v>46161.875</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Al Nassr</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Dhamk</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="3" t="n">
-        <v>46161.875</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Al Riyadh</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Al Akhdoud</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI32" s="3" t="n">
-        <v>46161.875</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Al Feiha</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Al Hilal</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI33" s="3" t="n">
-        <v>46161.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="R20" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.76</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R22" t="n">
-        <v>4.33</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.76</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R21" t="n">
-        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>4.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>4.46</v>
       </c>
       <c r="R19" t="n">
-        <v>3.46</v>
+        <v>1.76</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.02</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.52</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.46</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>3.46</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>4.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>4.46</v>
       </c>
       <c r="R22" t="n">
-        <v>3.46</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>4.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>4.46</v>
       </c>
       <c r="R19" t="n">
-        <v>3.46</v>
+        <v>1.76</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="R20" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.52</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.46</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>3.46</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.52</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.46</v>
+        <v>3.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.76</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>4.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.86</v>
+        <v>4.46</v>
       </c>
       <c r="R19" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.52</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.46</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>1.76</v>
+        <v>3.46</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="R22" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>3.36</v>
+        <v>2.31</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>4.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.86</v>
+        <v>4.46</v>
       </c>
       <c r="R22" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>2.31</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>5.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R19" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>4.02</v>
       </c>
       <c r="R20" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>4.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.86</v>
+        <v>4.46</v>
       </c>
       <c r="R21" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.52</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.46</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>3.46</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R15" t="n">
-        <v>3.36</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>3.36</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.76</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="R22" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,70 +1204,70 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,52 +1276,52 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1473,52 +1473,52 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1795,70 +1795,70 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>3.36</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>5.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>3.36</v>
+        <v>2.31</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>4.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>4.46</v>
       </c>
       <c r="R19" t="n">
-        <v>3.46</v>
+        <v>1.76</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.02</v>
+        <v>3.77</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>3.36</v>
+        <v>2.31</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R20" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>4.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.86</v>
+        <v>4.46</v>
       </c>
       <c r="R22" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA7" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>3.36</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.36</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4.33</v>
-      </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>3.36</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>2.31</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.77</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,70 +1204,70 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X4" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI4" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,52 +1276,52 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA7" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R15" t="n">
-        <v>3.36</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>3.36</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="R20" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R21" t="n">
-        <v>4.33</v>
-      </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS4" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X5" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI5" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.3</v>
@@ -1879,7 +1879,7 @@
         <v>2.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AV7" t="n">
         <v>3.1</v>
@@ -3174,124 +3174,124 @@
         <v>2.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3371,13 +3371,13 @@
         <v>1.55</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3568,13 +3568,13 @@
         <v>3.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,28 +3598,28 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -3628,10 +3628,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         <v>2.31</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,28 +3795,28 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -3825,10 +3825,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>4.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.86</v>
+        <v>4.46</v>
       </c>
       <c r="R20" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.52</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.46</v>
+        <v>3.86</v>
       </c>
       <c r="R21" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X4" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI4" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>3.36</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>2.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI16" t="n">
         <v>3.8</v>
       </c>
-      <c r="R16" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AJ16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R19" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.52</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.46</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>1.76</v>
+        <v>3.46</v>
       </c>
       <c r="S20" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>4.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.86</v>
+        <v>4.46</v>
       </c>
       <c r="R21" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>4.02</v>
       </c>
       <c r="R22" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5144,124 +5144,124 @@
         <v>3.52</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS4" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X5" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI5" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.55</v>
       </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI16" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AJ16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AN16" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>5.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,55 +3780,55 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="R19" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="R20" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.02</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X4" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI4" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.04</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI15" t="n">
         <v>3.8</v>
       </c>
-      <c r="R15" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
         <v>1.58</v>
@@ -3610,16 +3610,16 @@
         <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -3628,10 +3628,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.55</v>
       </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI17" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AJ17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AN17" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4.33</v>
-      </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS4" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X5" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI5" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>3.36</v>
+        <v>2.31</v>
       </c>
       <c r="S16" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Y16" t="n">
         <v>1.58</v>
@@ -3610,16 +3610,16 @@
         <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -3628,10 +3628,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Y17" t="n">
         <v>1.58</v>
@@ -3807,16 +3807,16 @@
         <v>2.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -3825,10 +3825,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="R20" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X4" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI4" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.04</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA7" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.52</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.46</v>
+        <v>3.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="R21" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>4.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>4.46</v>
       </c>
       <c r="R22" t="n">
-        <v>3.46</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS4" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X5" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI5" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.04</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>3.36</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>2.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI17" t="n">
         <v>3.8</v>
       </c>
-      <c r="R17" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AJ17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4.33</v>
-      </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.77</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.52</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.46</v>
+        <v>3.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="S22" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI15" t="n">
         <v>3.8</v>
       </c>
-      <c r="R15" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
         <v>1.58</v>
@@ -3610,16 +3610,16 @@
         <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -3628,10 +3628,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.55</v>
       </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI17" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AJ17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AN17" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.52</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.46</v>
+        <v>3.86</v>
       </c>
       <c r="R20" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>4.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.86</v>
+        <v>4.46</v>
       </c>
       <c r="R22" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X4" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI4" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.04</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.69</v>
+        <v>1.43</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.53</v>
+        <v>4.6</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>5.8</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA7" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>3.36</v>
+        <v>2.31</v>
       </c>
       <c r="S16" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Y16" t="n">
         <v>1.58</v>
@@ -3610,16 +3610,16 @@
         <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -3628,10 +3628,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Y17" t="n">
         <v>1.58</v>
@@ -3807,16 +3807,16 @@
         <v>2.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -3825,10 +3825,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>4.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>4.46</v>
       </c>
       <c r="R19" t="n">
-        <v>3.46</v>
+        <v>1.76</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS4" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X5" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI5" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.69</v>
+        <v>1.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.53</v>
+        <v>4.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.03</v>
+        <v>5.8</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.43</v>
+        <v>3.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="R7" t="n">
-        <v>5.8</v>
+        <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.04</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3380,10 +3380,10 @@
         <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X15" t="n">
         <v>2.12</v>
@@ -3392,13 +3392,13 @@
         <v>1.56</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
         <v>1.14</v>
@@ -3440,55 +3440,55 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC15" t="n">
         <v>1.68</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
         <v>1.93</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,43 +3559,43 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
         <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC16" t="n">
         <v>1.13</v>
@@ -3610,82 +3610,82 @@
         <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
       </c>
       <c r="BC16" t="n">
         <v>1.65</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,43 +3756,43 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>3.36</v>
+        <v>2.31</v>
       </c>
       <c r="S17" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Y17" t="n">
         <v>1.58</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
         <v>1.13</v>
@@ -3807,82 +3807,82 @@
         <v>2.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC17" t="n">
         <v>1.65</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>4.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>4.46</v>
       </c>
       <c r="R20" t="n">
-        <v>3.46</v>
+        <v>1.76</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.02</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X4" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI4" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.55</v>
       </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AI15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.21</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
         <v>1.58</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AY15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.33</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>5.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="X17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
         <v>1.58</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.77</v>
+        <v>4.62</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.67</v>
+        <v>1.39</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4.33</v>
-      </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.46</v>
+        <v>4.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.76</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="R21" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="R22" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.95</v>
+        <v>3.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.6</v>
+        <v>12.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS4" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="X5" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI5" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.43</v>
+        <v>3.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="R6" t="n">
-        <v>5.8</v>
+        <v>2.03</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.04</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.69</v>
+        <v>1.43</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.53</v>
+        <v>4.6</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>5.8</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA7" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.72</v>
+        <v>5.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="X15" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
         <v>1.58</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.77</v>
+        <v>4.62</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.67</v>
+        <v>1.39</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,43 +3559,43 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>3.36</v>
+        <v>2.31</v>
       </c>
       <c r="S16" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="X16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Y16" t="n">
         <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
         <v>1.13</v>
@@ -3610,82 +3610,82 @@
         <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AY16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
         <v>1.65</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>3.36</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>2.43</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U17" t="n">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="X17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>5.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AH17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>1.53</v>
       </c>
-      <c r="AI17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ17" t="n">
+      <c r="BA17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC17" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.52</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.46</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>3.46</v>
       </c>
       <c r="S19" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4.33</v>
-      </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.77</v>
+        <v>4.02</v>
       </c>
       <c r="R21" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.69</v>
+        <v>1.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.53</v>
+        <v>4.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.03</v>
+        <v>5.8</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>5.51</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA6" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.43</v>
+        <v>3.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="R7" t="n">
-        <v>5.8</v>
+        <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.51</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.39</v>
+        <v>3.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.63</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.49</v>
+        <v>1.29</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.04</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>3.36</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>2.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="X15" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.33</v>
+        <v>5.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AB15" t="n">
         <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AH15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>1.53</v>
       </c>
-      <c r="AI15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="BA15" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.36</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>2.43</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>3.4</v>
+        <v>1.96</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="X17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AB17" t="n">
         <v>1.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.88</v>
+        <v>3.54</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.79</v>
+        <v>3.08</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AX17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BA17" t="n">
         <v>1.39</v>
       </c>
-      <c r="AY17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.44</v>
-      </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.02</v>
+        <v>3.86</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="R22" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -998,28 +998,28 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.45</v>
+        <v>5.05</v>
       </c>
       <c r="R3" t="n">
-        <v>9.15</v>
+        <v>7.6</v>
       </c>
       <c r="S3" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>7.55</v>
+        <v>7.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="X3" t="n">
         <v>2.16</v>
@@ -1028,25 +1028,25 @@
         <v>1.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA3" t="n">
         <v>1.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AD3" t="n">
         <v>5.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AG3" t="n">
         <v>2.17</v>
@@ -1055,16 +1055,16 @@
         <v>1.61</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.21</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
         <v>1.08</v>
@@ -1115,13 +1115,13 @@
         <v>1.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BD3" t="n">
         <v>5.35</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="BF3" t="n">
         <v>1.28</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
         <v>1.44</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.69</v>
       </c>
-      <c r="AG4" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>3.25</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.05</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.9</v>
       </c>
-      <c r="X5" t="n">
-        <v>2.73</v>
-      </c>
       <c r="Y5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN5" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.02</v>
+        <v>2.31</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1598,13 +1598,13 @@
         <v>5.8</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="U6" t="n">
-        <v>5.51</v>
+        <v>5.25</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
@@ -1613,13 +1613,13 @@
         <v>3.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Y6" t="n">
         <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.14</v>
@@ -1631,91 +1631,91 @@
         <v>1.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.39</v>
+        <v>7.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AH6" t="n">
         <v>1.67</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.04</v>
+        <v>3.5</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.04</v>
+        <v>3.76</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="BA6" t="n">
         <v>3.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1795,124 +1795,124 @@
         <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="X7" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.64</v>
+        <v>3.84</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.27</v>
       </c>
-      <c r="AI7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL7" t="n">
+      <c r="AN7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC7" t="n">
         <v>1.93</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.17</v>
-      </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3165,16 +3165,16 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
         <v>2.2</v>
@@ -3183,61 +3183,61 @@
         <v>2.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="X14" t="n">
         <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Z14" t="n">
         <v>6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB14" t="n">
         <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,13 +3246,13 @@
         <v>1.22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AT14" t="n">
         <v>2.83</v>
@@ -3261,37 +3261,37 @@
         <v>3.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AY14" t="n">
         <v>1.34</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.15</v>
+        <v>3.96</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>3.36</v>
+        <v>2.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG15" t="n">
         <v>2.48</v>
       </c>
-      <c r="U15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK15" t="n">
         <v>1.57</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.79</v>
+        <v>2.93</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AY15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.17</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC15" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.31</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>4.43</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="X16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV16" t="n">
         <v>2.08</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH16" t="n">
+      <c r="AW16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>1.55</v>
       </c>
-      <c r="AI16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BA16" t="n">
-        <v>2.67</v>
+        <v>3.44</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>5.85</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
         <v>1.21</v>
@@ -3780,10 +3780,10 @@
         <v>3.68</v>
       </c>
       <c r="X17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="Z17" t="n">
         <v>4.33</v>
@@ -3807,49 +3807,49 @@
         <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.53</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AT17" t="n">
         <v>3.54</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="AV17" t="n">
         <v>2.24</v>
@@ -3858,28 +3858,28 @@
         <v>1.75</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AZ17" t="n">
         <v>4.62</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="BB17" t="n">
         <v>1.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD17" t="n">
         <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="BF17" t="n">
         <v>1.33</v>
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>5.76</v>
+        <v>4.6</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>3.46</v>
+        <v>4.4</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.52</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.46</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.76</v>
+        <v>3.61</v>
       </c>
       <c r="S20" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.15</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.61</v>
-      </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS21" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="R21" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5144,52 +5144,52 @@
         <v>3.52</v>
       </c>
       <c r="S24" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="V24" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
         <v>3.6</v>
       </c>
       <c r="X24" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA24" t="n">
         <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.63</v>
       </c>
       <c r="AI24" t="n">
         <v>4.4</v>
@@ -5204,64 +5204,64 @@
         <v>2.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.9</v>
+        <v>4.17</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BB24" t="n">
         <v>1.14</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.43</v>
+        <v>3.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="R6" t="n">
-        <v>5.8</v>
+        <v>2.03</v>
       </c>
       <c r="S6" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>3.68</v>
+        <v>2.85</v>
       </c>
       <c r="X6" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.33</v>
+        <v>3.84</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.66</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.23</v>
+        <v>3.48</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AI6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AL6" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.63</v>
+        <v>1.27</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="AW6" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.29</v>
+        <v>2.43</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.5</v>
+        <v>3.84</v>
       </c>
       <c r="BE6" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.69</v>
+        <v>1.43</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.53</v>
+        <v>4.6</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>5.8</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1.96</v>
       </c>
       <c r="T7" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.85</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.84</v>
+        <v>7.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.87</v>
+        <v>2.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.48</v>
+        <v>2.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.22</v>
+        <v>3.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.27</v>
+        <v>2.63</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>1.18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.66</v>
+        <v>3.76</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.43</v>
+        <v>1.29</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.72</v>
+        <v>3.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.84</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,40 +3559,40 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.43</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="X16" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AB16" t="n">
         <v>1.02</v>
@@ -3601,91 +3601,91 @@
         <v>1.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.25</v>
+        <v>3.28</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.99</v>
+        <v>1.08</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.55</v>
+        <v>4.62</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.44</v>
+        <v>1.35</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,40 +3756,40 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.12</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="S17" t="n">
-        <v>5.85</v>
+        <v>2.27</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>4.43</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="X17" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>5.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.02</v>
@@ -3798,91 +3798,91 @@
         <v>1.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.11</v>
+        <v>2.43</v>
       </c>
       <c r="AH17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW17" t="n">
         <v>1.69</v>
       </c>
-      <c r="AI17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM17" t="n">
+      <c r="AX17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.14</v>
       </c>
-      <c r="AN17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC17" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R19" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>3.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.71</v>
+        <v>3.61</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.66</v>
       </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="S18" t="n">
         <v>2.17</v>
@@ -3992,10 +3992,10 @@
         <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AE18" t="n">
         <v>1.82</v>
@@ -4004,13 +4004,13 @@
         <v>1.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AH18" t="n">
         <v>1.35</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.16</v>
+        <v>6.5</v>
       </c>
       <c r="AJ18" t="n">
         <v>1.1</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>3.61</v>
+        <v>4.8</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>3.61</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
         <v>3.25</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
-      </c>
       <c r="V4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM4" t="n">
         <v>1.33</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AN4" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AS4" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="X5" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AF5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG5" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AL5" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="U15" t="n">
-        <v>3.18</v>
+        <v>4.43</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.49</v>
+        <v>1.99</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.67</v>
+        <v>3.44</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="S16" t="n">
-        <v>5.85</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>3.18</v>
       </c>
       <c r="V16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.21</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.33</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,40 +3756,40 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4.43</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="X17" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AB17" t="n">
         <v>1.02</v>
@@ -3798,91 +3798,91 @@
         <v>1.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.25</v>
+        <v>3.28</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.99</v>
+        <v>1.08</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.55</v>
+        <v>4.62</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.44</v>
+        <v>1.35</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="R19" t="n">
-        <v>4.33</v>
+        <v>1.71</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.1</v>
+        <v>3.66</v>
       </c>
       <c r="R20" t="n">
-        <v>1.71</v>
+        <v>3.61</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.66</v>
       </c>
-      <c r="Z20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>3.61</v>
+        <v>4.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="S3" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="T3" t="n">
         <v>2.62</v>
@@ -1043,16 +1043,16 @@
         <v>5.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AG3" t="n">
         <v>2.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AI3" t="n">
         <v>3.7</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z4" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI4" t="n">
-        <v>8.5</v>
+        <v>5.89</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>3.25</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN5" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AS5" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.69</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.53</v>
+        <v>4.65</v>
       </c>
       <c r="R6" t="n">
-        <v>2.03</v>
+        <v>5.7</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.85</v>
+        <v>3.78</v>
       </c>
       <c r="X6" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.26</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.27</v>
+        <v>2.64</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.66</v>
+        <v>3.76</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.43</v>
+        <v>1.29</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.72</v>
+        <v>3.45</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.84</v>
+        <v>5.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.43</v>
+        <v>3.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="R7" t="n">
-        <v>5.8</v>
+        <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>1.96</v>
+        <v>4.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="U7" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>3.68</v>
+        <v>2.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.33</v>
+        <v>3.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.66</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.23</v>
+        <v>3.74</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.5</v>
+        <v>6.22</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.63</v>
+        <v>1.3</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>1.18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="AW7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC7" t="n">
         <v>2</v>
       </c>
-      <c r="AX7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BD7" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S14" t="n">
         <v>3.3</v>
@@ -3204,19 +3204,19 @@
         <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AH14" t="n">
         <v>1.33</v>
@@ -3234,10 +3234,10 @@
         <v>2.13</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,13 +3246,13 @@
         <v>1.22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AT14" t="n">
         <v>2.83</v>
@@ -3261,13 +3261,13 @@
         <v>3.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AY14" t="n">
         <v>1.34</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.43</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="X15" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AB15" t="n">
         <v>1.02</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM15" t="n">
         <v>1.14</v>
       </c>
-      <c r="AD15" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AN15" t="n">
-        <v>1.99</v>
+        <v>1.07</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.55</v>
+        <v>4.62</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.44</v>
+        <v>1.35</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.45</v>
+        <v>5.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -3574,13 +3574,13 @@
         <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="X16" t="n">
         <v>2.5</v>
@@ -3604,7 +3604,7 @@
         <v>4.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AF16" t="n">
         <v>2.07</v>
@@ -3616,7 +3616,7 @@
         <v>1.41</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.75</v>
+        <v>4.96</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.12</v>
@@ -3625,13 +3625,13 @@
         <v>1.57</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AM16" t="n">
         <v>1.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.35</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AT16" t="n">
         <v>3.64</v>
@@ -3661,7 +3661,7 @@
         <v>1.71</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AY16" t="n">
         <v>1.2</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.12</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>3.97</v>
       </c>
       <c r="S17" t="n">
-        <v>5.85</v>
+        <v>2.27</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>4.43</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="X17" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AB17" t="n">
         <v>1.02</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.14</v>
       </c>
-      <c r="AD17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC17" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.71</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>4.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>1.79</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5147,55 +5147,55 @@
         <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="V24" t="n">
         <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="X24" t="n">
         <v>2.35</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA24" t="n">
         <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AD24" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI24" t="n">
         <v>4.5</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK24" t="n">
         <v>1.5</v>
@@ -5204,10 +5204,10 @@
         <v>2.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5243,19 +5243,19 @@
         <v>1.49</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BC24" t="n">
         <v>1.82</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE24" t="n">
         <v>2.02</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
         <v>3.25</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN4" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z5" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AI5" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG5" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AL5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI5" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="S18" t="n">
         <v>2.17</v>
@@ -3974,16 +3974,16 @@
         <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X18" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Y18" t="n">
         <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA18" t="n">
         <v>1.09</v>
@@ -3992,10 +3992,10 @@
         <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AE18" t="n">
         <v>1.82</v>
@@ -4004,13 +4004,13 @@
         <v>1.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="AH18" t="n">
         <v>1.35</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AJ18" t="n">
         <v>1.1</v>
@@ -4067,19 +4067,19 @@
         <v>2.88</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
-        <v>3.61</v>
+        <v>4.8</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.03</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>3.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.79</v>
+        <v>3.61</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>4.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>4.8</v>
+        <v>1.79</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,124 +1204,124 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z4" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AI4" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG4" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AL4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI4" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>3.25</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN5" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.12</v>
+        <v>2.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="S15" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS15" t="n">
         <v>2.62</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AT15" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.21</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.33</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.45</v>
+        <v>3.97</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="U16" t="n">
-        <v>2.99</v>
+        <v>4.43</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.91</v>
+        <v>3.28</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.19</v>
       </c>
-      <c r="AD16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.64</v>
+        <v>3.88</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.93</v>
+        <v>2.79</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.67</v>
+        <v>3.44</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>5.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.97</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>2.27</v>
+        <v>5.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>4.43</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="X17" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AB17" t="n">
         <v>1.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BA17" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW17" t="n">
+      <c r="BB17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC17" t="n">
         <v>1.66</v>
       </c>
-      <c r="AX17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.84</v>
-      </c>
       <c r="BD17" t="n">
-        <v>4.45</v>
+        <v>5.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>4.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
-        <v>4.8</v>
+        <v>1.79</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>3.61</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.03</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.97</v>
       </c>
       <c r="R22" t="n">
-        <v>1.79</v>
+        <v>5.1</v>
       </c>
       <c r="S22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI24"/>
+  <dimension ref="A1:BI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46161.57291666666</v>
+        <v>46161.5625</v>
       </c>
     </row>
     <row r="14">
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46161.58333333334</v>
+        <v>46161.57291666666</v>
       </c>
     </row>
     <row r="15">
@@ -3309,27 +3309,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,134 +3362,134 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="X15" t="n">
         <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.19</v>
       </c>
-      <c r="AD15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BG15" t="n">
         <v>0</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46161.60416666666</v>
+        <v>46161.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>3.97</v>
+        <v>2.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>4.43</v>
+        <v>2.99</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>3.28</v>
+        <v>2.91</v>
       </c>
       <c r="X16" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AD16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD16" t="n">
         <v>4.2</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.45</v>
-      </c>
       <c r="BE16" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>5.2</v>
+        <v>3.97</v>
       </c>
       <c r="S18" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="T18" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="U18" t="n">
-        <v>5.52</v>
+        <v>4.43</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="X18" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AB18" t="n">
         <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.29</v>
+        <v>2.43</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>4.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="AM18" t="n">
         <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.81</v>
+        <v>2.46</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.95</v>
+        <v>3.88</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AX18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BA18" t="n">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46161.625</v>
+        <v>46161.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD19" t="n">
         <v>3.6</v>
       </c>
-      <c r="R19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46161.64583333334</v>
+        <v>46161.625</v>
       </c>
     </row>
     <row r="20">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>3.66</v>
       </c>
       <c r="R20" t="n">
-        <v>1.79</v>
+        <v>3.6</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>1.66</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
-        <v>5.1</v>
+        <v>4.52</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46161.66666666666</v>
+        <v>46161.64583333334</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,141 +5135,338 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="3" t="n">
+        <v>46161.66666666666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.5</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>2.25</v>
       </c>
-      <c r="U24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="U25" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.25</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>3.3</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>2.35</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Y25" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="Z25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA25" t="n">
         <v>1.11</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AB25" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AC25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
         <v>1.13</v>
       </c>
-      <c r="AD24" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI24" t="n">
+      <c r="AQ25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU25" t="n">
         <v>4.5</v>
       </c>
-      <c r="AJ24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN24" t="n">
+      <c r="AV25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC25" t="n">
         <v>1.82</v>
       </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE24" t="n">
+      <c r="BD25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE25" t="n">
         <v>2.02</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BF25" t="n">
         <v>1.28</v>
       </c>
-      <c r="BG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI24" s="3" t="n">
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="3" t="n">
         <v>46161.67708333334</v>
       </c>
     </row>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -998,31 +998,31 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="R3" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="S3" t="n">
         <v>1.61</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="X3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Y3" t="n">
         <v>1.62</v>
@@ -1040,37 +1040,37 @@
         <v>1.13</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AE3" t="n">
         <v>1.45</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AH3" t="n">
         <v>1.63</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1115,16 +1115,16 @@
         <v>1.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC4" t="n">
         <v>1.35</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AD4" t="n">
-        <v>3.95</v>
+        <v>3.26</v>
       </c>
       <c r="AE4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AL4" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.92</v>
+        <v>3.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG5" t="n">
         <v>3.25</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AH5" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z5" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AI5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG5" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AL5" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.41</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>5.7</v>
+        <v>2.04</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>6.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.43</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.06</v>
+        <v>2.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>2.3</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="BA6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BF6" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.32</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.69</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.53</v>
+        <v>4.55</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>5.3</v>
       </c>
       <c r="S7" t="n">
-        <v>4.05</v>
+        <v>1.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.09</v>
+        <v>2.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.1</v>
+        <v>4.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.57</v>
+        <v>7.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.74</v>
+        <v>2.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.22</v>
+        <v>3.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.3</v>
+        <v>2.52</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>1.18</v>
       </c>
       <c r="AQ7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.37</v>
       </c>
-      <c r="AR7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.43</v>
-      </c>
       <c r="BA7" t="n">
-        <v>1.72</v>
+        <v>3.45</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>5.35</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.63</v>
+        <v>2.11</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2998,10 +2998,10 @@
         <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB13" t="n">
         <v>1</v>
@@ -3365,10 +3365,10 @@
         <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="S15" t="n">
         <v>3.28</v>
@@ -3425,10 +3425,10 @@
         <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AM15" t="n">
         <v>1.28</v>
@@ -3443,13 +3443,13 @@
         <v>1.23</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AT15" t="n">
         <v>2.8</v>
@@ -3458,13 +3458,13 @@
         <v>3.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AW15" t="n">
         <v>2.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AY15" t="n">
         <v>1.38</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>5.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.99</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.91</v>
+        <v>3.68</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.96</v>
+        <v>3.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.45</v>
+        <v>1.07</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.78</v>
+        <v>4.62</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.67</v>
+        <v>1.35</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.12</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>3.97</v>
       </c>
       <c r="S17" t="n">
-        <v>5.9</v>
+        <v>2.27</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>4.43</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="X17" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AB17" t="n">
         <v>1.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.11</v>
+        <v>2.43</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AM17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.14</v>
       </c>
-      <c r="AN17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC17" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.3</v>
+        <v>4.45</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>3.97</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>4.43</v>
+        <v>2.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
-        <v>3.28</v>
+        <v>2.91</v>
       </c>
       <c r="X18" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AD18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD18" t="n">
         <v>4.2</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.45</v>
-      </c>
       <c r="BE18" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>3.6</v>
+        <v>4.52</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.15</v>
+        <v>3.66</v>
       </c>
       <c r="R21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.66</v>
       </c>
-      <c r="S21" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="R22" t="n">
-        <v>4.52</v>
+        <v>5.15</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.64</v>
+        <v>4.36</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="R23" t="n">
-        <v>5.15</v>
+        <v>1.7</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
         <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="S25" t="n">
         <v>2.5</v>
@@ -5347,7 +5347,7 @@
         <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="V25" t="n">
         <v>1.25</v>
@@ -5362,7 +5362,7 @@
         <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA25" t="n">
         <v>1.11</v>
@@ -5374,16 +5374,16 @@
         <v>1.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AF25" t="n">
         <v>2.39</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AH25" t="n">
         <v>1.55</v>
@@ -5404,46 +5404,46 @@
         <v>1.32</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.5</v>
+        <v>4.17</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="BB25" t="n">
         <v>1.15</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA6" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="BB6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BE6" t="n">
         <v>2.11</v>
       </c>
-      <c r="AT6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.49</v>
+        <v>3.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.55</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>5.3</v>
+        <v>2.04</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>2.09</v>
       </c>
       <c r="U7" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="X7" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AL7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>2.3</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="BA7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3165,112 +3165,112 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.12</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="S16" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>2.85</v>
       </c>
       <c r="V16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.21</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.33</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.2</v>
+        <v>5.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AF17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV17" t="n">
         <v>2.23</v>
       </c>
-      <c r="AG17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH17" t="n">
+      <c r="AW17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX17" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL17" t="n">
+      <c r="AY17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BE17" t="n">
         <v>2.21</v>
       </c>
-      <c r="AM17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BF17" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="U18" t="n">
-        <v>2.99</v>
+        <v>4.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.96</v>
+        <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.45</v>
+        <v>2.16</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AV18" t="n">
         <v>2.15</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AY18" t="n">
         <v>1.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.67</v>
+        <v>3.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="S19" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>5.52</v>
+        <v>5.38</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="X19" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.7</v>
+        <v>6.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
         <v>1.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" t="n">
         <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>2.88</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4350,10 +4350,10 @@
         <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R20" t="n">
-        <v>4.52</v>
+        <v>4.05</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.99</v>
+        <v>4.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.66</v>
+        <v>4.3</v>
       </c>
       <c r="R21" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>5.15</v>
+        <v>3.24</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.36</v>
+        <v>1.61</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="R23" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.7</v>
       </c>
-      <c r="S23" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AF23" t="n">
         <v>2.1</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,112 +5135,112 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1210,13 +1210,13 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="X4" t="n">
         <v>3.05</v>
@@ -1228,10 +1228,10 @@
         <v>7.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
         <v>1.35</v>
@@ -1243,10 +1243,10 @@
         <v>2.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.82</v>
+        <v>4.46</v>
       </c>
       <c r="AH4" t="n">
         <v>1.22</v>
@@ -1267,46 +1267,46 @@
         <v>1.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BB4" t="n">
         <v>1.25</v>
@@ -1392,16 +1392,16 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
         <v>2.11</v>
@@ -1422,7 +1422,7 @@
         <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.04</v>
@@ -1440,7 +1440,7 @@
         <v>1.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
         <v>3.25</v>
@@ -1464,7 +1464,7 @@
         <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1476,16 +1476,16 @@
         <v>1.41</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="AV5" t="n">
         <v>2.6</v>
@@ -1494,16 +1494,16 @@
         <v>1.99</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AZ5" t="n">
         <v>2.35</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
         <v>1.22</v>
@@ -1518,7 +1518,7 @@
         <v>1.69</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="R6" t="n">
         <v>5.3</v>
@@ -1601,22 +1601,22 @@
         <v>1.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="U6" t="n">
         <v>5.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
         <v>3.68</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Z6" t="n">
         <v>4.55</v>
@@ -1631,7 +1631,7 @@
         <v>1.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.28</v>
+        <v>7.33</v>
       </c>
       <c r="AE6" t="n">
         <v>1.47</v>
@@ -1643,10 +1643,10 @@
         <v>2.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.25</v>
@@ -1661,43 +1661,43 @@
         <v>1.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.76</v>
+        <v>3.94</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="BA6" t="n">
         <v>3.45</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="S7" t="n">
         <v>4.1</v>
@@ -1852,13 +1852,13 @@
         <v>1.65</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1897,7 +1897,7 @@
         <v>2.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="BB7" t="n">
         <v>1.22</v>
@@ -1906,7 +1906,7 @@
         <v>1.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="BE7" t="n">
         <v>1.76</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z10" t="n">
         <v>7</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
         <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.05</v>
+        <v>2.88</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.49</v>
+        <v>3.68</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.24</v>
+        <v>1.65</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>1.58</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="AS10" t="n">
         <v>2.53</v>
@@ -2476,7 +2476,7 @@
         <v>2.21</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AX10" t="n">
         <v>1.43</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.67</v>
+        <v>1.76</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="X11" t="n">
-        <v>3.02</v>
+        <v>2.41</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
         <v>1.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.88</v>
+        <v>4.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.09</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.68</v>
+        <v>2.49</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.65</v>
+        <v>3.24</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.58</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AS11" t="n">
         <v>2.53</v>
@@ -2673,7 +2673,7 @@
         <v>2.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AX11" t="n">
         <v>1.43</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="R13" t="n">
         <v>2.9</v>
@@ -2998,25 +2998,25 @@
         <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB13" t="n">
         <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
         <v>3.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>3.18</v>
@@ -3046,40 +3046,40 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AT13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="BB13" t="n">
         <v>1.22</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>6.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>6.45</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
       <c r="U16" t="n">
-        <v>2.85</v>
+        <v>1.67</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="W16" t="n">
-        <v>3.05</v>
+        <v>3.92</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AB16" t="n">
         <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.8</v>
+        <v>5.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.07</v>
+        <v>2.74</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.5</v>
+        <v>3.04</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
         <v>1.57</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC16" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>6.5</v>
+        <v>1.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
         <v>1.31</v>
       </c>
-      <c r="S17" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.89</v>
+        <v>1.55</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.32</v>
+        <v>3.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="X18" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.15</v>
+        <v>5.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
         <v>1.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.16</v>
+        <v>1.45</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.58</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,58 +4150,58 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>4.7</v>
+        <v>4.89</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="V19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="X19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.45</v>
+        <v>6.65</v>
       </c>
       <c r="AA19" t="n">
         <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AH19" t="n">
         <v>1.33</v>
@@ -4210,70 +4210,70 @@
         <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="BF19" t="n">
         <v>1.2</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="R20" t="n">
-        <v>4.05</v>
+        <v>5.25</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4544,19 +4544,19 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.36</v>
+        <v>4.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="S21" t="n">
         <v>4.45</v>
       </c>
       <c r="T21" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="U21" t="n">
         <v>2.1</v>
@@ -4565,19 +4565,19 @@
         <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AB21" t="n">
         <v>1.01</v>
@@ -4586,25 +4586,25 @@
         <v>1.12</v>
       </c>
       <c r="AD21" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AF21" t="n">
         <v>2.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK21" t="n">
         <v>1.5</v>
@@ -4613,10 +4613,10 @@
         <v>2.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>1.87</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AZ21" t="n">
         <v>3.05</v>
@@ -4658,19 +4658,19 @@
         <v>1.47</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="R22" t="n">
-        <v>3.24</v>
+        <v>4.42</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.05</v>
+        <v>3.66</v>
       </c>
       <c r="R23" t="n">
-        <v>4.46</v>
+        <v>3.6</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5332,34 +5332,34 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="R25" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="V25" t="n">
         <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="X25" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Z25" t="n">
         <v>5.4</v>
@@ -5374,28 +5374,28 @@
         <v>1.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.18</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AL25" t="n">
         <v>2.5</v>
@@ -5404,7 +5404,7 @@
         <v>1.32</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5440,22 +5440,22 @@
         <v>1.49</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BB25" t="n">
         <v>1.15</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.28</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.48</v>
+        <v>3.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>5.3</v>
+        <v>1.92</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="X6" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.55</v>
+        <v>6.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.33</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>2.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.71</v>
+        <v>5.75</v>
       </c>
       <c r="AJ6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN6" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.55</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.35</v>
+        <v>4.15</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.92</v>
+        <v>5.3</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.05</v>
+        <v>4.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.25</v>
+        <v>2.55</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>1.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AS7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BE7" t="n">
         <v>2.11</v>
       </c>
-      <c r="AT7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>6.5</v>
+        <v>1.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
         <v>1.31</v>
       </c>
-      <c r="S16" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.89</v>
+        <v>1.55</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.32</v>
+        <v>3.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="X17" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.15</v>
+        <v>5.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AH17" t="n">
         <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.16</v>
+        <v>1.45</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.58</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.37</v>
+        <v>6.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>6.45</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.85</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>3.05</v>
+        <v>3.92</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AB18" t="n">
         <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.8</v>
+        <v>5.65</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.07</v>
+        <v>2.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.5</v>
+        <v>3.04</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
         <v>1.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC18" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.61</v>
+        <v>4.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>5.25</v>
+        <v>1.65</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.57</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="R21" t="n">
-        <v>1.65</v>
+        <v>4.42</v>
       </c>
       <c r="S21" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="R22" t="n">
-        <v>4.42</v>
+        <v>5.25</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U4" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.46</v>
+        <v>3.25</v>
       </c>
       <c r="AH4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC4" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.36</v>
+        <v>3.92</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="V5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.35</v>
       </c>
-      <c r="W5" t="n">
-        <v>3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AD5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI5" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.92</v>
+        <v>3.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="R10" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>2.67</v>
+        <v>1.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="X10" t="n">
-        <v>3.02</v>
+        <v>2.41</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AB10" t="n">
         <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.88</v>
+        <v>4.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.09</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.68</v>
+        <v>2.49</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.65</v>
+        <v>3.24</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>1.58</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AS10" t="n">
         <v>2.53</v>
@@ -2476,7 +2476,7 @@
         <v>2.21</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AX10" t="n">
         <v>1.43</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z11" t="n">
         <v>7</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5</v>
-      </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
         <v>1.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.05</v>
+        <v>2.88</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.49</v>
+        <v>3.68</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.24</v>
+        <v>1.65</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.58</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="AS11" t="n">
         <v>2.53</v>
@@ -2673,7 +2673,7 @@
         <v>2.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AX11" t="n">
         <v>1.43</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.37</v>
+        <v>6.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>6.45</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
       <c r="U17" t="n">
-        <v>2.85</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>3.05</v>
+        <v>3.92</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AB17" t="n">
         <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.8</v>
+        <v>5.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.07</v>
+        <v>2.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.5</v>
+        <v>3.04</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
         <v>1.57</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC17" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>6.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
-        <v>6.45</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.74</v>
+        <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.67</v>
+        <v>2.85</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>3.92</v>
+        <v>3.05</v>
       </c>
       <c r="X18" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
         <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.65</v>
+        <v>3.8</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.74</v>
+        <v>2.07</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.04</v>
+        <v>5.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK18" t="n">
         <v>1.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.44</v>
+        <v>3.51</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.89</v>
+        <v>1.88</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.32</v>
+        <v>2.48</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.21</v>
+        <v>1.81</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.57</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="R20" t="n">
-        <v>1.65</v>
+        <v>4.42</v>
       </c>
       <c r="S20" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="R21" t="n">
-        <v>4.42</v>
+        <v>5.25</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.95</v>
+        <v>3.66</v>
       </c>
       <c r="R22" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>4.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.66</v>
+        <v>4.4</v>
       </c>
       <c r="R23" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Q3" t="n">
         <v>5.05</v>
       </c>
       <c r="R3" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="S3" t="n">
         <v>1.61</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
@@ -1022,13 +1022,13 @@
         <v>3.7</v>
       </c>
       <c r="X3" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA3" t="n">
         <v>1.12</v>
@@ -1040,19 +1040,19 @@
         <v>1.13</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.35</v>
+        <v>5.09</v>
       </c>
       <c r="AE3" t="n">
         <v>1.45</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AI3" t="n">
         <v>3.62</v>
@@ -1061,55 +1061,55 @@
         <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AM3" t="n">
         <v>1.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
         <v>1.09</v>
@@ -1124,7 +1124,7 @@
         <v>2.08</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1198,130 +1198,130 @@
         <v>2.42</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.25</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AK4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY4" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.92</v>
+        <v>3.52</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="Q5" t="n">
         <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG5" t="n">
         <v>3.13</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS5" t="n">
         <v>2.15</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>2.35</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BA5" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.36</v>
+        <v>3.98</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R6" t="n">
-        <v>1.92</v>
+        <v>5.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>1.91</v>
       </c>
       <c r="T6" t="n">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>5.35</v>
       </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z6" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.75</v>
+        <v>3.66</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.15</v>
+        <v>5.45</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.48</v>
+        <v>3.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>5.3</v>
+        <v>1.83</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>2.53</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>5.1</v>
+        <v>2.55</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="X7" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.55</v>
+        <v>5.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.33</v>
+        <v>4.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.19</v>
+        <v>2.72</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.71</v>
+        <v>5.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.55</v>
+        <v>1.31</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>1.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.71</v>
+        <v>2.43</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.35</v>
+        <v>4.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z10" t="n">
         <v>7</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.4</v>
+        <v>6.05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2476,7 +2476,7 @@
         <v>2.21</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AX10" t="n">
         <v>1.43</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>3.65</v>
+        <v>4.24</v>
       </c>
       <c r="S11" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="X11" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA11" t="n">
         <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.88</v>
       </c>
-      <c r="AE11" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN11" t="n">
         <v>1.66</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.65</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.58</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AS11" t="n">
         <v>2.53</v>
@@ -2673,7 +2673,7 @@
         <v>2.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AX11" t="n">
         <v>1.43</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3165,37 +3165,37 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>6.41</v>
+        <v>7.6</v>
       </c>
       <c r="V14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="X14" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AA14" t="n">
         <v>1.06</v>
@@ -3204,40 +3204,40 @@
         <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,16 +3279,16 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="BF14" t="n">
         <v>1.14</v>
@@ -3362,16 +3362,16 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="T15" t="n">
         <v>2.2</v>
@@ -3383,13 +3383,13 @@
         <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="X15" t="n">
         <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
         <v>6</v>
@@ -3407,34 +3407,34 @@
         <v>3.58</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
         <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.57</v>
+        <v>5.75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3443,28 +3443,28 @@
         <v>1.23</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AT15" t="n">
         <v>2.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AW15" t="n">
         <v>2.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AY15" t="n">
         <v>1.38</v>
@@ -3479,16 +3479,16 @@
         <v>1.18</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="BD15" t="n">
         <v>4.05</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="V16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
         <v>1.29</v>
       </c>
-      <c r="W16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AX16" t="n">
         <v>1.41</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>6.5</v>
+        <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R17" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
         <v>1.31</v>
-      </c>
-      <c r="S17" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.29</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.61</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.89</v>
+        <v>1.55</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.32</v>
+        <v>3.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.37</v>
+        <v>6.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>6.35</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>2.85</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AB18" t="n">
         <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.8</v>
+        <v>5.55</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.07</v>
+        <v>2.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.5</v>
+        <v>3.43</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="AM18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX18" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AY18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BA18" t="n">
         <v>1.22</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.48</v>
-      </c>
       <c r="BB18" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,49 +4150,49 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
         <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>4.89</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
         <v>5.44</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="X19" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AE19" t="n">
         <v>1.9</v>
@@ -4201,82 +4201,82 @@
         <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AM19" t="n">
         <v>1.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AR19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV19" t="n">
         <v>2.09</v>
       </c>
-      <c r="AS19" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AW19" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="R20" t="n">
-        <v>4.42</v>
+        <v>3.6</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>4.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.66</v>
+        <v>4.4</v>
       </c>
       <c r="R22" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.57</v>
+        <v>1.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.65</v>
+        <v>4.42</v>
       </c>
       <c r="S23" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.67</v>
+        <v>3.96</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W24" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="X24" t="n">
-        <v>3.68</v>
+        <v>4.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK24" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>2.21</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.04</v>
+        <v>3.01</v>
       </c>
       <c r="AS24" t="n">
         <v>4.44</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI25"/>
+  <dimension ref="A1:BI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,19 +804,19 @@
         <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R2" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="S2" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>4.16</v>
+        <v>3.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.65</v>
@@ -831,19 +831,19 @@
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB2" t="n">
         <v>1.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AE2" t="n">
         <v>2.83</v>
@@ -927,7 +927,7 @@
         <v>1.32</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1.41</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AR4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY4" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AZ4" t="n">
         <v>2.35</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BA4" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.52</v>
+        <v>3.98</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U5" t="n">
         <v>3.1</v>
       </c>
-      <c r="R5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.3</v>
-      </c>
       <c r="V5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.34</v>
       </c>
-      <c r="W5" t="n">
-        <v>3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.74</v>
+        <v>3.32</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.49</v>
+        <v>3.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>5.25</v>
+        <v>1.83</v>
       </c>
       <c r="S6" t="n">
-        <v>1.91</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>5.35</v>
+        <v>2.55</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="X6" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.45</v>
+        <v>5.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.65</v>
+        <v>4.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.17</v>
+        <v>2.72</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.66</v>
+        <v>5.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.64</v>
+        <v>1.31</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.71</v>
+        <v>2.43</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.45</v>
+        <v>4.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R7" t="n">
-        <v>1.83</v>
+        <v>5.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>1.91</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.55</v>
+        <v>5.35</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.95</v>
+        <v>4.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.1</v>
+        <v>7.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.72</v>
+        <v>2.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.4</v>
+        <v>3.66</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.31</v>
+        <v>2.64</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>1.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.43</v>
+        <v>2.71</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.25</v>
+        <v>5.45</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>3.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X8" t="n">
         <v>2.5</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,134 +2377,134 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>7.7</v>
+        <v>2.35</v>
       </c>
       <c r="S10" t="n">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2.16</v>
       </c>
-      <c r="U10" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AL10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46161.5</v>
+        <v>46161.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>4.24</v>
+        <v>7.7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.68</v>
+        <v>1.89</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>4.75</v>
+        <v>8.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="X11" t="n">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.66</v>
+        <v>2.89</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>2.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AX11" t="n">
         <v>1.43</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2718,27 +2718,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46161.54166666666</v>
+        <v>46161.5</v>
       </c>
     </row>
     <row r="13">
@@ -2915,27 +2915,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46161.5625</v>
+        <v>46161.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="R14" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="S14" t="n">
-        <v>2.12</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="X14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG14" t="n">
         <v>3.18</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AH14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AK14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
         <v>1.61</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT14" t="n">
         <v>3.1</v>
       </c>
-      <c r="AH14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>4.97</v>
-      </c>
       <c r="AU14" t="n">
-        <v>2.37</v>
+        <v>3.27</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.32</v>
+        <v>3.66</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="BF14" t="n">
         <v>1.14</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46161.57291666666</v>
+        <v>46161.5625</v>
       </c>
     </row>
     <row r="15">
@@ -3309,27 +3309,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.65</v>
+        <v>1.49</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR15" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AS15" t="n">
-        <v>2.18</v>
+        <v>3.34</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.8</v>
+        <v>4.97</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.7</v>
+        <v>2.37</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.05</v>
+        <v>3.32</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46161.58333333334</v>
+        <v>46161.57291666666</v>
       </c>
     </row>
     <row r="16">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="X16" t="n">
         <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.96</v>
+        <v>5.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.31</v>
+        <v>1.71</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.51</v>
+        <v>2.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.02</v>
+        <v>3.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.88</v>
+        <v>2.23</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46161.60416666666</v>
+        <v>46161.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -3756,76 +3756,76 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="R17" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="S17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="T17" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="U17" t="n">
-        <v>4.09</v>
+        <v>4.9</v>
       </c>
       <c r="V17" t="n">
         <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="X17" t="n">
         <v>2.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AA17" t="n">
         <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.54</v>
+        <v>4.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AN17" t="n">
         <v>2.19</v>
@@ -3840,10 +3840,10 @@
         <v>1.61</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AT17" t="n">
         <v>3.58</v>
@@ -3858,7 +3858,7 @@
         <v>1.72</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AY17" t="n">
         <v>1.21</v>
@@ -3870,19 +3870,19 @@
         <v>3.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,19 +3953,19 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>6.3</v>
+        <v>8.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>6.35</v>
+        <v>6.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
         <v>1.67</v>
@@ -3977,10 +3977,10 @@
         <v>4.1</v>
       </c>
       <c r="X18" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
         <v>4</v>
@@ -3995,7 +3995,7 @@
         <v>1.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AE18" t="n">
         <v>1.36</v>
@@ -4004,16 +4004,16 @@
         <v>2.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.43</v>
+        <v>3.05</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
         <v>1.65</v>
@@ -4022,7 +4022,7 @@
         <v>2.11</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AN18" t="n">
         <v>1.05</v>
@@ -4058,7 +4058,7 @@
         <v>1.27</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AZ18" t="n">
         <v>6.5</v>
@@ -4073,7 +4073,7 @@
         <v>1.59</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="BE18" t="n">
         <v>2.19</v>
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT19" t="n">
         <v>3.5</v>
       </c>
-      <c r="R19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.64</v>
-      </c>
       <c r="AU19" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AY19" t="n">
         <v>1.22</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.08</v>
+        <v>2.48</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46161.625</v>
+        <v>46161.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>1.66</v>
       </c>
-      <c r="AF20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46161.64583333334</v>
+        <v>46161.625</v>
       </c>
     </row>
     <row r="21">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.61</v>
+        <v>4.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>5.25</v>
+        <v>1.65</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.57</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="R22" t="n">
-        <v>1.65</v>
+        <v>4.42</v>
       </c>
       <c r="S22" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="R23" t="n">
-        <v>4.42</v>
+        <v>5.25</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,112 +5135,112 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.77</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.85</v>
+        <v>3.66</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="S24" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.15</v>
       </c>
-      <c r="X24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AG24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46161.66666666666</v>
+        <v>46161.64583333334</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,141 +5332,338 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>2.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.71</v>
+        <v>2.85</v>
       </c>
       <c r="R25" t="n">
-        <v>3.62</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>3.96</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="U25" t="n">
-        <v>4.14</v>
+        <v>3.2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="W25" t="n">
-        <v>3.28</v>
+        <v>2.15</v>
       </c>
       <c r="X25" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.56</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.14</v>
+        <v>1.69</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.59</v>
+        <v>2.98</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.37</v>
+        <v>1.31</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.54</v>
+        <v>1.08</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.52</v>
+        <v>2.45</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="AM25" t="n">
         <v>1.32</v>
       </c>
       <c r="AN25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="3" t="n">
+        <v>46161.66666666666</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN26" t="n">
         <v>1.85</v>
       </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AQ26" t="n">
         <v>1.33</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AR26" t="n">
         <v>1.71</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AS26" t="n">
         <v>1.94</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AT26" t="n">
         <v>2.44</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AU26" t="n">
         <v>4.17</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AV26" t="n">
         <v>3.02</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AW26" t="n">
         <v>2.26</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AX26" t="n">
         <v>1.8</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="AY26" t="n">
         <v>1.49</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="AZ26" t="n">
         <v>1.58</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BA26" t="n">
         <v>2.65</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BB26" t="n">
         <v>1.15</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BC26" t="n">
         <v>1.83</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BD26" t="n">
         <v>5.05</v>
       </c>
-      <c r="BE25" t="n">
+      <c r="BE26" t="n">
         <v>2.01</v>
       </c>
-      <c r="BF25" t="n">
+      <c r="BF26" t="n">
         <v>1.28</v>
       </c>
-      <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI25" s="3" t="n">
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
         <v>46161.67708333334</v>
       </c>
     </row>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U4" t="n">
         <v>3.1</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="V4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.34</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.74</v>
+        <v>3.32</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>1.41</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AR5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AZ5" t="n">
         <v>2.35</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BA5" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.52</v>
+        <v>3.98</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="S9" t="n">
-        <v>4.74</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="U9" t="n">
         <v>3.26</v>
       </c>
       <c r="V9" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="W9" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="X9" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.11</v>
+        <v>2.66</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.75</v>
+        <v>5.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AM9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
         <v>1.38</v>
       </c>
-      <c r="AN9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BC9" t="n">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.41</v>
+        <v>2.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
         <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>4.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="U10" t="n">
         <v>3.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W10" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="X10" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AK10" t="n">
-        <v>2.16</v>
+        <v>2.47</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>7.7</v>
+        <v>4.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.89</v>
+        <v>2.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>8.75</v>
+        <v>4.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="X11" t="n">
-        <v>2.05</v>
+        <v>2.96</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.05</v>
+        <v>6.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.89</v>
+        <v>1.66</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>2.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AX11" t="n">
         <v>1.43</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>4.24</v>
+        <v>7.7</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>1.89</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>4.75</v>
+        <v>8.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="X12" t="n">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.66</v>
+        <v>2.89</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>2.21</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AX12" t="n">
         <v>1.43</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.6</v>
+        <v>8.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.05</v>
+        <v>5.65</v>
       </c>
       <c r="R17" t="n">
-        <v>4.7</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.15</v>
+        <v>6.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>4.9</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="X17" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AB17" t="n">
         <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.1</v>
+        <v>5.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL17" t="n">
         <v>2.11</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AN17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BE17" t="n">
         <v>2.19</v>
       </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.88</v>
-      </c>
       <c r="BF17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>8.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.65</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>4.7</v>
       </c>
       <c r="S18" t="n">
-        <v>6.55</v>
+        <v>2.15</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="U18" t="n">
-        <v>1.67</v>
+        <v>4.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="X18" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AB18" t="n">
         <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.65</v>
+        <v>4.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.81</v>
+        <v>2.19</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.78</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>2.11</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.05</v>
+        <v>2.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.82</v>
+        <v>2</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.49</v>
+        <v>2.92</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.5</v>
+        <v>1.55</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.22</v>
+        <v>3.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.1</v>
+        <v>4.45</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="R22" t="n">
-        <v>4.42</v>
+        <v>3.6</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="R23" t="n">
-        <v>5.25</v>
+        <v>4.42</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.66</v>
+        <v>3.95</v>
       </c>
       <c r="R24" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -790,14 +790,14 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -987,90 +987,90 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.05</v>
+        <v>6.2</v>
       </c>
       <c r="R3" t="n">
-        <v>7.6</v>
+        <v>10.17</v>
       </c>
       <c r="S3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="T3" t="n">
-        <v>2.64</v>
+        <v>2.93</v>
       </c>
       <c r="U3" t="n">
-        <v>7.8</v>
+        <v>7.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.09</v>
+        <v>7.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.55</v>
+        <v>3.34</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.62</v>
+        <v>2.52</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.31</v>
+        <v>2.78</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.4</v>
+        <v>6.38</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.08</v>
+        <v>2.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,25 +1157,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1184,144 +1184,144 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.03</v>
+        <v>3.46</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
         <v>1.03</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AS4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>2.35</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.25</v>
       </c>
       <c r="BA4" t="n">
         <v>2.02</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.52</v>
+        <v>3.82</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,171 +1354,171 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="V5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.34</v>
       </c>
-      <c r="W5" t="n">
-        <v>3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.16</v>
+        <v>2.49</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.88</v>
+        <v>2.59</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.13</v>
+        <v>6.53</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AQ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.41</v>
       </c>
-      <c r="AR5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W6" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.1</v>
-      </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.1</v>
+        <v>4.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
         <v>1.88</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="BA6" t="n">
         <v>1.7</v>
       </c>
       <c r="BB6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF6" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,49 +1786,49 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="R7" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="T7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>5.35</v>
+        <v>4.85</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
         <v>1.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.65</v>
+        <v>5.62</v>
       </c>
       <c r="AE7" t="n">
         <v>1.44</v>
@@ -1837,82 +1837,82 @@
         <v>2.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.66</v>
+        <v>3.76</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>2.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.94</v>
+        <v>4.16</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U8" t="n">
         <v>3.5</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.37</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="W8" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC8" t="n">
-        <v>1.96</v>
+        <v>3.14</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.25</v>
+        <v>2.44</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,22 +2180,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.62</v>
@@ -2210,31 +2210,31 @@
         <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.1</v>
+        <v>11.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
         <v>1.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>3.71</v>
       </c>
       <c r="Q10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>2.6</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="X10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.2</v>
+        <v>1.96</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.41</v>
+        <v>4.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,34 +2574,34 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
-        <v>4.24</v>
+        <v>3.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="T11" t="n">
         <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>4.75</v>
+        <v>4.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="X11" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
         <v>6.7</v>
@@ -2610,43 +2610,43 @@
         <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2771,43 +2771,43 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>8.75</v>
+        <v>9.35</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="X12" t="n">
         <v>2.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AA12" t="n">
         <v>1.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
         <v>1.27</v>
@@ -2816,34 +2816,34 @@
         <v>3.14</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>2.21</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AX12" t="n">
         <v>1.43</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3362,34 +3362,34 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="U15" t="n">
-        <v>7.6</v>
+        <v>7.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="X15" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
         <v>6.9</v>
@@ -3398,43 +3398,43 @@
         <v>1.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>1.26</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="BF15" t="n">
         <v>1.14</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,31 +3953,31 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>4.7</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.46</v>
+        <v>2.19</v>
       </c>
       <c r="U18" t="n">
-        <v>4.9</v>
+        <v>2.82</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="X18" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="Y18" t="n">
         <v>1.51</v>
@@ -3992,94 +3992,94 @@
         <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX18" t="n">
         <v>1.43</v>
       </c>
-      <c r="AI18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ18" t="n">
+      <c r="AY18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.14</v>
       </c>
-      <c r="AK18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BC18" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BD18" t="n">
         <v>4.45</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,31 +4150,31 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
-        <v>2.45</v>
+        <v>4.7</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="T19" t="n">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="U19" t="n">
-        <v>2.82</v>
+        <v>4.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="X19" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="Y19" t="n">
         <v>1.51</v>
@@ -4189,94 +4189,94 @@
         <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AG19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS19" t="n">
         <v>2.63</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AT19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.15</v>
       </c>
-      <c r="AK19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BC19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BD19" t="n">
         <v>4.45</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.65</v>
+        <v>5.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.1</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AG21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="R22" t="n">
-        <v>3.6</v>
+        <v>4.42</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="R23" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.95</v>
+        <v>3.66</v>
       </c>
       <c r="R24" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5332,85 +5332,85 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="Q25" t="n">
         <v>2.85</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S25" t="n">
-        <v>3.96</v>
+        <v>3.54</v>
       </c>
       <c r="T25" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="V25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL25" t="n">
         <v>1.62</v>
       </c>
-      <c r="W25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AM25" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AQ25" t="n">
         <v>2.21</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1572,20 +1572,20 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1772,17 +1772,17 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1954,13 +1954,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1969,17 +1969,17 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.9</v>
-      </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA9" t="n">
         <v>1.62</v>
       </c>
-      <c r="W9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="BB9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.07</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2366,144 +2366,144 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.71</v>
+        <v>2.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="S10" t="n">
-        <v>4.47</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
-        <v>2.37</v>
+        <v>3.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="X10" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,22 +2574,22 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.61</v>
+        <v>1.99</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>4.97</v>
+        <v>9.35</v>
       </c>
       <c r="V11" t="n">
         <v>1.45</v>
@@ -2598,55 +2598,55 @@
         <v>2.47</v>
       </c>
       <c r="X11" t="n">
-        <v>2.92</v>
+        <v>2.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="BD11" t="n">
         <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="S12" t="n">
-        <v>1.99</v>
+        <v>2.61</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>9.35</v>
+        <v>4.97</v>
       </c>
       <c r="V12" t="n">
         <v>1.45</v>
@@ -2795,55 +2795,55 @@
         <v>2.47</v>
       </c>
       <c r="X12" t="n">
-        <v>2.05</v>
+        <v>2.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="BD12" t="n">
         <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.65</v>
+        <v>3.19</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>2.88</v>
       </c>
       <c r="V16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN16" t="n">
         <v>1.33</v>
       </c>
-      <c r="W16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AR16" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AY16" t="n">
         <v>1.38</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>8.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.65</v>
+        <v>3.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>2.62</v>
       </c>
       <c r="S17" t="n">
-        <v>6.55</v>
+        <v>2.92</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>2.69</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="X17" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>5.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.65</v>
+        <v>4.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.81</v>
+        <v>2.22</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AH17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AW17" t="n">
         <v>1.78</v>
       </c>
-      <c r="AI17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AX17" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AY17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.14</v>
       </c>
-      <c r="AZ17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BC17" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.1</v>
+        <v>4.55</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,28 +3953,28 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="T18" t="n">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="U18" t="n">
-        <v>2.82</v>
+        <v>4.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="X18" t="n">
         <v>2.36</v>
@@ -3983,100 +3983,100 @@
         <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
         <v>1.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.15</v>
+        <v>4.54</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.96</v>
+        <v>4.3</v>
       </c>
       <c r="AJ18" t="n">
         <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.48</v>
+        <v>3.82</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BD18" t="n">
         <v>4.45</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BF18" t="n">
         <v>1.24</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.05</v>
+        <v>5.35</v>
       </c>
       <c r="R19" t="n">
-        <v>4.7</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.15</v>
+        <v>5.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.46</v>
+        <v>2.79</v>
       </c>
       <c r="U19" t="n">
-        <v>4.9</v>
+        <v>1.76</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="X19" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AF19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BE19" t="n">
         <v>2.19</v>
       </c>
-      <c r="AG19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.88</v>
-      </c>
       <c r="BF19" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.57</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.4</v>
+        <v>3.66</v>
       </c>
       <c r="R23" t="n">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="S23" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>4.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.66</v>
+        <v>4.4</v>
       </c>
       <c r="R24" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1157,37 +1157,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.46</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="X4" t="n">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.72</v>
+        <v>2.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.8</v>
+        <v>2.59</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.2</v>
+        <v>6.53</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.41</v>
       </c>
-      <c r="AR4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,37 +1354,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>3.46</v>
       </c>
       <c r="R5" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.49</v>
+        <v>3.72</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.59</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.53</v>
+        <v>3.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AS5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>2.35</v>
       </c>
-      <c r="AT5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BA5" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.95</v>
+        <v>3.82</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2169,144 +2169,144 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>2.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>4.63</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM9" t="n">
         <v>1.35</v>
       </c>
-      <c r="W9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AN9" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.94</v>
+        <v>2.79</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.14</v>
+        <v>2.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2366,144 +2366,144 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="AH10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA10" t="n">
         <v>1.62</v>
       </c>
-      <c r="W10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="BB10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.07</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,22 +2536,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2560,36 +2560,36 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.99</v>
+        <v>2.61</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>9.35</v>
+        <v>4.97</v>
       </c>
       <c r="V11" t="n">
         <v>1.45</v>
@@ -2598,55 +2598,55 @@
         <v>2.47</v>
       </c>
       <c r="X11" t="n">
-        <v>2.05</v>
+        <v>2.92</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
         <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,60 +2733,60 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.61</v>
+        <v>1.99</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>4.97</v>
+        <v>9.35</v>
       </c>
       <c r="V12" t="n">
         <v>1.45</v>
@@ -2795,55 +2795,55 @@
         <v>2.47</v>
       </c>
       <c r="X12" t="n">
-        <v>2.92</v>
+        <v>2.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="BD12" t="n">
         <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3148,129 +3148,129 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W14" t="n">
         <v>2.81</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.85</v>
-      </c>
       <c r="X14" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="AA14" t="n">
         <v>1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD14" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AI14" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AM14" t="n">
         <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AZ14" t="n">
         <v>1.75</v>
@@ -3279,19 +3279,19 @@
         <v>2.53</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -3351,21 +3351,21 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
         <v>5.25</v>
@@ -3374,16 +3374,16 @@
         <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>7.11</v>
+        <v>6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="X15" t="n">
         <v>2.96</v>
@@ -3398,43 +3398,43 @@
         <v>1.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC15" t="n">
         <v>1.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3530,32 +3530,32 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3727,32 +3727,32 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3942,144 +3942,144 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>5.35</v>
       </c>
       <c r="R18" t="n">
-        <v>4.2</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.15</v>
+        <v>5.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.46</v>
+        <v>2.79</v>
       </c>
       <c r="U18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT18" t="n">
         <v>4.33</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.62</v>
-      </c>
       <c r="AU18" t="n">
-        <v>2.94</v>
+        <v>2.49</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.52</v>
+        <v>6.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.82</v>
+        <v>1.22</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.45</v>
+        <v>6.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,171 +4112,171 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>1.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.35</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z19" t="n">
         <v>5.75</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="AA19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY19" t="n">
         <v>1.2</v>
       </c>
-      <c r="W19" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>6.5</v>
+        <v>1.52</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.22</v>
+        <v>3.82</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.1</v>
+        <v>4.45</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -4330,150 +4330,150 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL20" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U20" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AM20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC20" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.94</v>
+        <v>4.45</v>
       </c>
       <c r="R22" t="n">
-        <v>4.42</v>
+        <v>4.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U23" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="V23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W23" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI23" t="n">
         <v>3.6</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4.57</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.65</v>
+        <v>3.18</v>
       </c>
       <c r="S24" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5335,73 +5335,73 @@
         <v>2.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
         <v>2.45</v>
       </c>
       <c r="S25" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="U25" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="X25" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="Y25" t="n">
         <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AL25" t="n">
         <v>1.62</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AN25" t="n">
         <v>1.36</v>
@@ -5416,7 +5416,7 @@
         <v>2.21</v>
       </c>
       <c r="AR25" t="n">
-        <v>3.01</v>
+        <v>4.04</v>
       </c>
       <c r="AS25" t="n">
         <v>4.44</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="S26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AT26" t="n">
         <v>2.4</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="AU26" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1945,22 +1945,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X8" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,22 +2142,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2166,93 +2166,93 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
         <v>5</v>
       </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AK9" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.79</v>
+        <v>3.14</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2536,19 +2536,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -2557,39 +2557,39 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
         <v>4</v>
       </c>
-      <c r="N11" t="n">
-        <v>8</v>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.61</v>
+        <v>1.99</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>4.97</v>
+        <v>9.35</v>
       </c>
       <c r="V11" t="n">
         <v>1.45</v>
@@ -2598,55 +2598,55 @@
         <v>2.47</v>
       </c>
       <c r="X11" t="n">
-        <v>2.92</v>
+        <v>2.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="BD11" t="n">
         <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,19 +2733,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
@@ -2754,16 +2754,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="S12" t="n">
-        <v>1.99</v>
+        <v>2.61</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>9.35</v>
+        <v>4.97</v>
       </c>
       <c r="V12" t="n">
         <v>1.45</v>
@@ -2795,55 +2795,55 @@
         <v>2.47</v>
       </c>
       <c r="X12" t="n">
-        <v>2.05</v>
+        <v>2.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="BD12" t="n">
         <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -4506,25 +4506,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -4533,24 +4533,24 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="R21" t="n">
-        <v>5.26</v>
+        <v>3.18</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,51 +4703,51 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>4.8</v>
+        <v>5.26</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4927,144 +4927,144 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="N23" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.7</v>
+        <v>1.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="S23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,22 +5097,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -5121,147 +5121,147 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>4.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>3.18</v>
+        <v>1.67</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5321,14 +5321,14 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5500,32 +5500,32 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P26" t="n">

--- a/jogos_2026-05-19.xlsx
+++ b/jogos_2026-05-19.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1972,144 +1972,144 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="N8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG8" t="n">
         <v>3</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="AH8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA8" t="n">
         <v>1.62</v>
       </c>
-      <c r="W8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="BB8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BF8" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.07</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,22 +2142,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2166,13 +2166,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W9" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -2363,147 +2363,147 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>4.63</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BD10" t="n">
         <v>2.44</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.14</v>
-      </c>
       <c r="BE10" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,19 +2536,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -2574,22 +2574,22 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.99</v>
+        <v>2.61</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>9.35</v>
+        <v>4.97</v>
       </c>
       <c r="V11" t="n">
         <v>1.45</v>
@@ -2598,55 +2598,55 @@
         <v>2.47</v>
       </c>
       <c r="X11" t="n">
-        <v>2.05</v>
+        <v>2.92</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
         <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,19 +2733,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
@@ -2754,39 +2754,39 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="n">
         <v>4</v>
       </c>
-      <c r="N12" t="n">
-        <v>8</v>
-      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.61</v>
+        <v>1.99</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>4.97</v>
+        <v>9.35</v>
       </c>
       <c r="V12" t="n">
         <v>1.45</v>
@@ -2795,55 +2795,55 @@
         <v>2.47</v>
       </c>
       <c r="X12" t="n">
-        <v>2.92</v>
+        <v>2.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="BD12" t="n">
         <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3718,171 +3718,171 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
+        <v>9</v>
+      </c>
+      <c r="N17" t="n">
         <v>4</v>
       </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.22</v>
       </c>
       <c r="AG17" t="n">
         <v>2.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AY17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.24</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.26</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,37 +4112,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="R19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD19" t="n">
         <v>4.2</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.54</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AG19" t="n">
         <v>2.55</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.82</v>
+        <v>2.22</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,171 +4506,171 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>7</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="V21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BD21" t="n">
         <v>5</v>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R21" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,37 +4703,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="R22" t="n">
-        <v>5.26</v>
+        <v>4.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,37 +4900,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>4.8</v>
+        <v>5.26</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,171 +5097,171 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="M24" t="n">
-        <v>7</v>
-      </c>
-      <c r="N24" t="n">
-        <v>6</v>
-      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4.7</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.67</v>
+        <v>3.18</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
